--- a/artfynd/A 9253-2026 artfynd.xlsx
+++ b/artfynd/A 9253-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72896721</v>
+        <v>72896723</v>
       </c>
       <c r="B2" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111175</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>219677</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605410.2506069106</v>
+        <v>605410</v>
       </c>
       <c r="R2" t="n">
-        <v>6289908.215326387</v>
+        <v>6289908</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,19 +747,9 @@
           <t>2018-08-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-08-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,19 +773,18 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>72896723</v>
+        <v>72896721</v>
       </c>
       <c r="B3" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106155</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219677</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605410.2506069106</v>
+        <v>605410</v>
       </c>
       <c r="R3" t="n">
-        <v>6289908.215326387</v>
+        <v>6289908</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +853,9 @@
           <t>2018-08-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-08-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +879,11 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9253-2026 artfynd.xlsx
+++ b/artfynd/A 9253-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72896723</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,8 +894,17 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72896721</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>